--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_106_R11.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_106_R11.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2834</v>
+        <v>5.476</v>
       </c>
       <c r="E2" t="n">
-        <v>3.614</v>
+        <v>3.8067</v>
       </c>
       <c r="F2" t="n">
         <v>1.6693</v>
@@ -610,10 +610,10 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0.1926</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2513</v>
+        <v>-0.0587</v>
       </c>
       <c r="U2" t="n">
         <v>0.2513</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. SMITS</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.487</v>
+        <v>3.2229</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3679</v>
+        <v>0.9518</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1191</v>
+        <v>2.2711</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4904</v>
+        <v>2.4757</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4766</v>
+        <v>-0.6662</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0138</v>
+        <v>3.1419</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2019</v>
+        <v>2.8974</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2351</v>
+        <v>-0.0434</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9669</v>
+        <v>2.9409</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7115</v>
+        <v>-0.4218</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7584</v>
+        <v>-0.6227</v>
       </c>
       <c r="O3" t="n">
-        <v>0.047</v>
+        <v>0.201</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>3.0154</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3908</v>
+        <v>-0.1986</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2715</v>
+        <v>-0.554</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1193</v>
+        <v>0.3554</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9304</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1444</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>R. SMITS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1044</v>
+        <v>2.242</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1694</v>
+        <v>2.3246</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9351</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4757</v>
+        <v>2.4904</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6662</v>
+        <v>1.4766</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1419</v>
+        <v>1.0138</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8974</v>
+        <v>3.2019</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0434</v>
+        <v>2.2351</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9409</v>
+        <v>0.9669</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4218</v>
+        <v>-0.7115</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6227</v>
+        <v>-0.7584</v>
       </c>
       <c r="O4" t="n">
-        <v>0.201</v>
+        <v>0.047</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0154</v>
+        <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.317</v>
+        <v>1.1459</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3364</v>
+        <v>0.2282</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0193</v>
+        <v>0.9177</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.9304</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9431</v>
+        <v>2.1625</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4867</v>
+        <v>0.8405</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4564</v>
+        <v>1.322</v>
       </c>
       <c r="G5" t="n">
         <v>1.0539</v>
@@ -844,13 +844,13 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1933</v>
+        <v>0.4127</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.224</v>
+        <v>0.1298</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4173</v>
+        <v>0.2829</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0668</v>
+        <v>0.1512</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3477</v>
+        <v>-0.2298</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4145</v>
+        <v>0.3809</v>
       </c>
       <c r="G6" t="n">
         <v>0.3266</v>
@@ -922,13 +922,13 @@
         <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2763</v>
+        <v>0.3607</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4257</v>
+        <v>0.3921</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5361</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.6543</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9669</v>
+        <v>-2.7742</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1871</v>
+        <v>2.1199</v>
       </c>
       <c r="G7" t="n">
         <v>-0.183</v>
@@ -1000,13 +1000,13 @@
         <v>2.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2926</v>
+        <v>-0.1672</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.44</v>
       </c>
       <c r="U7" t="n">
-        <v>0.34</v>
+        <v>0.2728</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5361</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8747</v>
+        <v>-0.8239</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6506</v>
+        <v>-0.7178</v>
       </c>
       <c r="G8" t="n">
         <v>0.4075</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.21</v>
+        <v>-0.1592</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0141</v>
+        <v>-0.0532</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. DESSERT</t>
+          <t>J. LOYD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4102</v>
+        <v>-2.0914</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.56</v>
+        <v>-3.2861</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1498</v>
+        <v>1.1948</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1439</v>
+        <v>-3.5437</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-1.1044</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4886</v>
+        <v>-2.4393</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1779</v>
+        <v>-2.8214</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1043</v>
+        <v>-0.1779</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0736</v>
+        <v>-2.6436</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3219</v>
+        <v>-0.7222</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7369</v>
+        <v>-0.9265</v>
       </c>
       <c r="O9" t="n">
-        <v>0.415</v>
+        <v>0.2042</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.7112</v>
+        <v>-1.3917</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7001</v>
+        <v>0.058</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6201</v>
+        <v>-0.1452</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08</v>
+        <v>0.2032</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6468</v>
+        <v>0.9304</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6468</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0824</v>
+        <v>-2.3183</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0227</v>
+        <v>-2.2586</v>
       </c>
       <c r="F10" t="n">
         <v>-0.0597</v>
@@ -1234,10 +1234,10 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1652</v>
+        <v>-0.0707</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2636</v>
+        <v>0.0277</v>
       </c>
       <c r="U10" t="n">
         <v>-0.0984</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. LOYD</t>
+          <t>B. DESSERT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1489</v>
+        <v>-2.4045</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2429</v>
+        <v>-3.6216</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0939</v>
+        <v>1.217</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.5437</v>
+        <v>-0.1439</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1044</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4393</v>
+        <v>0.4886</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.8214</v>
+        <v>0.1779</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1779</v>
+        <v>0.1043</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.6436</v>
+        <v>0.0736</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7222</v>
+        <v>-0.3219</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9265</v>
+        <v>-0.7369</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2042</v>
+        <v>0.415</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4639</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0004</v>
+        <v>0.7057</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1019</v>
+        <v>0.5586</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1024</v>
+        <v>0.1472</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9304</v>
+        <v>-0.6468</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0722</v>
+        <v>-0.6468</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.588800000000003</v>
+        <v>4.962200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7262</v>
+        <v>-4.3528</v>
       </c>
       <c r="F12" t="n">
-        <v>9.3149</v>
+        <v>9.314900000000002</v>
       </c>
       <c r="G12" t="n">
-        <v>4.718000000000002</v>
+        <v>4.718</v>
       </c>
       <c r="H12" t="n">
         <v>-1.5728</v>
@@ -1366,7 +1366,7 @@
         <v>8.042399999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2754</v>
+        <v>3.275400000000001</v>
       </c>
       <c r="L12" t="n">
         <v>4.767</v>
@@ -1375,7 +1375,7 @@
         <v>-3.3245</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.848</v>
+        <v>-4.848000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1.5236</v>
@@ -1390,16 +1390,16 @@
         <v>15.0769</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9065</v>
+        <v>2.2799</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7643999999999999</v>
+        <v>-0.3911</v>
       </c>
       <c r="U12" t="n">
         <v>2.671</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2836000000000002</v>
+        <v>0.2836000000000003</v>
       </c>
       <c r="W12" t="n">
         <v>5.392100000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>S. JOVIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5978</v>
+        <v>4.2218</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9919</v>
+        <v>3.269</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.394</v>
+        <v>0.9528</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1619</v>
+        <v>3.4985</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0301</v>
+        <v>1.3805</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1318</v>
+        <v>2.118</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9548</v>
+        <v>3.2843</v>
       </c>
       <c r="K13" t="n">
-        <v>0.08400000000000001</v>
+        <v>1.163</v>
       </c>
       <c r="L13" t="n">
-        <v>2.8708</v>
+        <v>2.1212</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2071</v>
+        <v>0.2142</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0539</v>
+        <v>0.2175</v>
       </c>
       <c r="O13" t="n">
-        <v>0.261</v>
+        <v>-0.0033</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8096</v>
+        <v>-0.6684</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1246</v>
+        <v>-0.1571</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.315</v>
+        <v>-0.5113</v>
       </c>
       <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="X13" t="n">
         <v>-0.1418</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.0722</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-1.214</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. JOVIC</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4748</v>
+        <v>3.0074</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6792</v>
+        <v>3.1662</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7956</v>
+        <v>-0.1588</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4985</v>
+        <v>3.1619</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3805</v>
+        <v>0.0301</v>
       </c>
       <c r="I14" t="n">
-        <v>2.118</v>
+        <v>3.1318</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2843</v>
+        <v>2.9548</v>
       </c>
       <c r="K14" t="n">
-        <v>1.163</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>2.1212</v>
+        <v>2.8708</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2142</v>
+        <v>0.2071</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2175</v>
+        <v>-0.0539</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0033</v>
+        <v>0.261</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4154</v>
+        <v>0.2192</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7468</v>
+        <v>0.2989</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6686</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1418</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8953</v>
+        <v>0.7564</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8215</v>
+        <v>0.9958</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0738</v>
+        <v>-0.2394</v>
       </c>
       <c r="G15" t="n">
         <v>-1.3475</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9233</v>
+        <v>0.7844</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4525</v>
+        <v>-0.3732</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4708</v>
+        <v>1.1576</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5361</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0505</v>
+        <v>0.0725</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9196</v>
+        <v>-1.1556</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8692</v>
+        <v>1.2281</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0616</v>
@@ -1702,13 +1702,13 @@
         <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3822</v>
+        <v>0.5052</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5623</v>
+        <v>0.3264</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1801</v>
+        <v>0.1788</v>
       </c>
       <c r="V16" t="n">
         <v>0.7886</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. MCCORMACK</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7478</v>
+        <v>-0.4638</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3665</v>
+        <v>-0.5713</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6187</v>
+        <v>0.1075</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3031</v>
+        <v>-1.227</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7347</v>
+        <v>0.0276</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4316</v>
+        <v>-1.2546</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.182</v>
+        <v>1.1318</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9845</v>
+        <v>0.911</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1975</v>
+        <v>0.2208</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8789</v>
+        <v>-2.3588</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2499</v>
+        <v>-0.8834</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6291</v>
+        <v>-1.4755</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.232</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3233</v>
+        <v>-0.0048</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9752</v>
+        <v>-0.4558</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6519</v>
+        <v>0.4509</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5361</v>
+        <v>0.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
         <v>-0.5361</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>I. MIKE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.02</v>
+        <v>-1.0666</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1611</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1411</v>
+        <v>-0.3917</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.227</v>
+        <v>-0.7889</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0276</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2546</v>
+        <v>-1.4154</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1318</v>
+        <v>1.184</v>
       </c>
       <c r="K18" t="n">
-        <v>0.911</v>
+        <v>1.385</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2208</v>
+        <v>-0.201</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3588</v>
+        <v>-1.9729</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8834</v>
+        <v>-0.7584</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4755</v>
+        <v>-1.2144</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5515</v>
+        <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5819</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0455</v>
+        <v>-0.9157</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4846</v>
+        <v>0.3339</v>
       </c>
       <c r="V18" t="n">
         <v>0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. MIKE</t>
+          <t>X. RATHAN-MAYES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3089</v>
+        <v>-1.403</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0287</v>
+        <v>-1.5881</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2801</v>
+        <v>0.185</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7889</v>
+        <v>-2.1502</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.1921</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4154</v>
+        <v>-2.3423</v>
       </c>
       <c r="J19" t="n">
-        <v>1.184</v>
+        <v>-0.9989</v>
       </c>
       <c r="K19" t="n">
-        <v>1.385</v>
+        <v>1.1294</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.201</v>
+        <v>-2.1283</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9729</v>
+        <v>-1.1513</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7584</v>
+        <v>-0.9373</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2144</v>
+        <v>-0.214</v>
       </c>
       <c r="P19" t="n">
+        <v>1.1598</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.232</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-2.5515</v>
-      </c>
       <c r="R19" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.5544</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2696</v>
+        <v>-0.4991</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4455</v>
+        <v>-0.0553</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="W19" t="n">
-        <v>1.6083</v>
+        <v>0.1418</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. HOLLATZ</t>
+          <t>D. MCCORMACK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4142</v>
+        <v>-1.4898</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0043</v>
+        <v>-2.3101</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5901</v>
+        <v>0.8204</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0744</v>
+        <v>-0.3031</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.054</v>
+        <v>-0.7347</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0205</v>
+        <v>0.4316</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8094</v>
+        <v>-1.182</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6855</v>
+        <v>-0.9845</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1239</v>
+        <v>-0.1975</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2651</v>
+        <v>0.8789</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3684</v>
+        <v>0.2499</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8966</v>
+        <v>0.6291</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1964</v>
+        <v>-0.4187</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0351</v>
+        <v>0.0316</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2315</v>
+        <v>-0.4503</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. RATHAN-MAYES</t>
+          <t>J. HOLLATZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.606</v>
+        <v>-1.5328</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0599</v>
+        <v>-2.3581</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4539</v>
+        <v>0.8253</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1502</v>
+        <v>-2.0744</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1921</v>
+        <v>-1.054</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3423</v>
+        <v>-1.0205</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9989</v>
+        <v>-0.8094</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1294</v>
+        <v>-0.6855</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.1283</v>
+        <v>-0.1239</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1513</v>
+        <v>-1.2651</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9373</v>
+        <v>-0.3684</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.214</v>
+        <v>-0.8966</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7573</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9709</v>
+        <v>-0.389</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2135</v>
+        <v>0.4668</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>S. DINWIDDIE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3722</v>
+        <v>-2.9204</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7593</v>
+        <v>-3.9183</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3871</v>
+        <v>0.998</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1236</v>
+        <v>-1.3023</v>
       </c>
       <c r="H22" t="n">
-        <v>0.299</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.4226</v>
+        <v>-1.9409</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.9275</v>
+        <v>-0.2874</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0707</v>
+        <v>0.8605</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.9982</v>
+        <v>-1.148</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8038999999999999</v>
+        <v>-1.0148</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2283</v>
+        <v>-0.222</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5756</v>
+        <v>-0.7929</v>
       </c>
       <c r="P22" t="n">
-        <v>0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-3.7112</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3917</v>
+        <v>2.5515</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9445</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6721</v>
+        <v>-0.4558</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2724</v>
+        <v>0.5335</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. DINWIDDIE</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0371</v>
+        <v>-2.9841</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5081</v>
+        <v>-4.1696</v>
       </c>
       <c r="F23" t="n">
-        <v>0.471</v>
+        <v>1.1855</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3023</v>
+        <v>-2.1236</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.299</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9409</v>
+        <v>-2.4226</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2874</v>
+        <v>-2.9275</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8605</v>
+        <v>0.0707</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.148</v>
+        <v>-2.9982</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0148</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.222</v>
+        <v>0.2283</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7929</v>
+        <v>0.5756</v>
       </c>
       <c r="P23" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-3.7112</v>
-      </c>
       <c r="R23" t="n">
-        <v>2.5515</v>
+        <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0389</v>
+        <v>-0.5564</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0455</v>
+        <v>-0.0824</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0066</v>
+        <v>-0.474</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.588800000000001</v>
+        <v>-3.802400000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.314900000000002</v>
+        <v>-9.315</v>
       </c>
       <c r="F24" t="n">
-        <v>4.7264</v>
+        <v>5.5127</v>
       </c>
       <c r="G24" t="n">
         <v>-4.7182</v>
@@ -2308,13 +2308,13 @@
         <v>-1.5239</v>
       </c>
       <c r="M24" t="n">
-        <v>-8.042400000000001</v>
+        <v>-8.042399999999999</v>
       </c>
       <c r="N24" t="n">
         <v>-3.2754</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.766999999999999</v>
+        <v>-4.767</v>
       </c>
       <c r="P24" t="n">
         <v>2.3194</v>
@@ -2326,13 +2326,13 @@
         <v>17.3965</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9064</v>
+        <v>-1.1202</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.6709</v>
+        <v>-2.6712</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7645000000000003</v>
+        <v>1.5509</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2836000000000001</v>
@@ -2341,7 +2341,7 @@
         <v>5.1085</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.392100000000001</v>
+        <v>-5.3921</v>
       </c>
     </row>
   </sheetData>
